--- a/poc/output/to-be/K-Tieout_결과_샘플제조_2025.xlsx
+++ b/poc/output/to-be/K-Tieout_결과_샘플제조_2025.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>401건 / 9,918,452,830원</t>
+          <t>402건 / 10,006,425,330원</t>
         </is>
       </c>
     </row>
@@ -3986,32 +3986,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>한결산업(주)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="10" t="n">
         <v>468234470</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>380261970</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>87972500</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="10" t="n">
+        <v>468234470</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>EX-07</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5152,10 +5156,10 @@
         <v>2551537690</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>2392236350</v>
+        <v>2480208850</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>159301340</v>
+        <v>71328840</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -29559,14 +29563,22 @@
       <c r="H429" s="10" t="n">
         <v>87972500</v>
       </c>
-      <c r="I429" s="11" t="n"/>
-      <c r="J429" s="11" t="inlineStr"/>
+      <c r="I429" s="11" t="inlineStr"/>
+      <c r="J429" s="11" t="inlineStr">
+        <is>
+          <t>입금완료</t>
+        </is>
+      </c>
       <c r="K429" s="11" t="inlineStr">
         <is>
           <t>일자·금액 일치</t>
         </is>
       </c>
-      <c r="L429" s="11" t="inlineStr"/>
+      <c r="L429" s="11" t="inlineStr">
+        <is>
+          <t>√√√</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="11" t="inlineStr">
